--- a/Routes.xlsx
+++ b/Routes.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eugk\Documents\iot\project\code\Pan\BR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eugk\Documents\iot\project\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F02CBA-965E-492B-B2C8-F0AEE033B5D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99469319-808E-4651-9AE7-A8DBE8DE98E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E451EE4A-2127-43C9-9A50-5536E739BF9B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="186">
   <si>
     <t>Intracom</t>
   </si>
@@ -594,33 +594,6 @@
   </si>
   <si>
     <t>University of Patras Chancellors Office</t>
-  </si>
-  <si>
-    <t>13:38:00 PM</t>
-  </si>
-  <si>
-    <t>13:39:00 PM</t>
-  </si>
-  <si>
-    <t>13:40:00 AM</t>
-  </si>
-  <si>
-    <t>13:41:00 AM</t>
-  </si>
-  <si>
-    <t>13:42:00 AM</t>
-  </si>
-  <si>
-    <t>13:43:00 PM</t>
-  </si>
-  <si>
-    <t>13:43:20 AM</t>
-  </si>
-  <si>
-    <t>13:43:30 AM</t>
-  </si>
-  <si>
-    <t>13:44:00 AM</t>
   </si>
 </sst>
 </file>
@@ -1146,13 +1119,13 @@
         <v>0.56666666666666665</v>
       </c>
       <c r="I5" s="2">
-        <v>0.23333333333333331</v>
+        <v>0.69166666666666676</v>
       </c>
       <c r="J5" s="2">
-        <v>0.23333333333333331</v>
+        <v>0.81666666666666676</v>
       </c>
       <c r="K5" s="2">
-        <v>0.23333333333333331</v>
+        <v>0.94166666666666676</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
@@ -1242,13 +1215,13 @@
         <v>0.56736111111111109</v>
       </c>
       <c r="I8" s="4">
-        <v>0.23402777777777781</v>
+        <v>0.69236111111111109</v>
       </c>
       <c r="J8" s="4">
-        <v>0.23402777777777781</v>
+        <v>0.81736111111111109</v>
       </c>
       <c r="K8" s="4">
-        <v>0.23402777777777781</v>
+        <v>0.94236111111111109</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
@@ -1334,17 +1307,17 @@
       <c r="G11" s="2">
         <v>0.44305555555555554</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>186</v>
+      <c r="H11" s="2">
+        <v>0.56805555555555554</v>
       </c>
       <c r="I11" s="2">
-        <v>0.23472222222222219</v>
+        <v>0.69305555555555554</v>
       </c>
       <c r="J11" s="2">
-        <v>0.23472222222222219</v>
+        <v>0.81805555555555554</v>
       </c>
       <c r="K11" s="2">
-        <v>0.23472222222222219</v>
+        <v>0.94305555555555554</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.3">
@@ -1462,17 +1435,17 @@
       <c r="G15" s="2">
         <v>0.44375000000000003</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>187</v>
+      <c r="H15" s="2">
+        <v>0.56874999999999998</v>
       </c>
       <c r="I15" s="2">
-        <v>0.23541666666666669</v>
+        <v>0.69374999999999998</v>
       </c>
       <c r="J15" s="2">
-        <v>0.23541666666666669</v>
+        <v>0.81874999999999998</v>
       </c>
       <c r="K15" s="2">
-        <v>0.23541666666666669</v>
+        <v>0.94374999999999998</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.3">
@@ -1558,17 +1531,17 @@
       <c r="G18" s="2">
         <v>0.44444444444444442</v>
       </c>
-      <c r="H18" s="2" t="s">
-        <v>188</v>
+      <c r="H18" s="2">
+        <v>0.56944444444444442</v>
       </c>
       <c r="I18" s="2">
-        <v>0.23611111111111113</v>
+        <v>0.69444444444444453</v>
       </c>
       <c r="J18" s="2">
-        <v>0.23611111111111113</v>
+        <v>0.81944444444444453</v>
       </c>
       <c r="K18" s="2">
-        <v>0.23611111111111113</v>
+        <v>0.94444444444444453</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.3">
@@ -1654,17 +1627,17 @@
       <c r="G21" s="5">
         <v>0.44513888888888892</v>
       </c>
-      <c r="H21" s="5" t="s">
-        <v>189</v>
+      <c r="H21" s="5">
+        <v>0.57013888888888886</v>
       </c>
       <c r="I21" s="5">
-        <v>0.23680555555555557</v>
+        <v>0.69513888888888886</v>
       </c>
       <c r="J21" s="5">
-        <v>0.23680555555555557</v>
+        <v>0.82013888888888886</v>
       </c>
       <c r="K21" s="5">
-        <v>0.23680555555555557</v>
+        <v>0.94513888888888886</v>
       </c>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.3">
@@ -1782,17 +1755,17 @@
       <c r="G25" s="2">
         <v>0.4458333333333333</v>
       </c>
-      <c r="H25" s="2" t="s">
-        <v>190</v>
+      <c r="H25" s="2">
+        <v>0.5708333333333333</v>
       </c>
       <c r="I25" s="2">
-        <v>0.23750000000000002</v>
+        <v>0.6958333333333333</v>
       </c>
       <c r="J25" s="2">
-        <v>0.23750000000000002</v>
+        <v>0.8208333333333333</v>
       </c>
       <c r="K25" s="2">
-        <v>0.23750000000000002</v>
+        <v>0.9458333333333333</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.3">
@@ -1910,17 +1883,17 @@
       <c r="G29" s="2">
         <v>0.4465277777777778</v>
       </c>
-      <c r="H29" s="2" t="s">
-        <v>191</v>
+      <c r="H29" s="2">
+        <v>0.57152777777777775</v>
       </c>
       <c r="I29" s="2">
-        <v>0.23819444444444446</v>
+        <v>0.69652777777777775</v>
       </c>
       <c r="J29" s="2">
-        <v>0.23819444444444446</v>
+        <v>0.82152777777777775</v>
       </c>
       <c r="K29" s="2">
-        <v>0.23819444444444446</v>
+        <v>0.94652777777777775</v>
       </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.3">
@@ -2006,17 +1979,17 @@
       <c r="G32" s="2">
         <v>0.44675925925925924</v>
       </c>
-      <c r="H32" s="2" t="s">
-        <v>192</v>
+      <c r="H32" s="2">
+        <v>0.57175925925925919</v>
       </c>
       <c r="I32" s="2">
-        <v>0.23842592592592593</v>
+        <v>0.69675925925925919</v>
       </c>
       <c r="J32" s="2">
-        <v>0.23842592592592593</v>
+        <v>0.82175925925925919</v>
       </c>
       <c r="K32" s="2">
-        <v>0.23842592592592593</v>
+        <v>0.94675925925925919</v>
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.3">
@@ -2102,17 +2075,17 @@
       <c r="G35" s="2">
         <v>0.44687499999999997</v>
       </c>
-      <c r="H35" s="2" t="s">
-        <v>193</v>
+      <c r="H35" s="2">
+        <v>0.57187500000000002</v>
       </c>
       <c r="I35" s="2">
-        <v>0.23854166666666665</v>
+        <v>0.69687500000000002</v>
       </c>
       <c r="J35" s="2">
-        <v>0.23854166666666665</v>
+        <v>0.82187500000000002</v>
       </c>
       <c r="K35" s="2">
-        <v>0.23854166666666665</v>
+        <v>0.94687500000000002</v>
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.3">
@@ -2262,17 +2235,17 @@
       <c r="G40" s="2">
         <v>0.44722222222222219</v>
       </c>
-      <c r="H40" s="2" t="s">
-        <v>194</v>
+      <c r="H40" s="2">
+        <v>0.57222222222222219</v>
       </c>
       <c r="I40" s="2">
-        <v>0.2388888888888889</v>
+        <v>0.6972222222222223</v>
       </c>
       <c r="J40" s="2">
-        <v>0.2388888888888889</v>
+        <v>0.8222222222222223</v>
       </c>
       <c r="K40" s="2">
-        <v>0.2388888888888889</v>
+        <v>0.9472222222222223</v>
       </c>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.3">
@@ -2359,16 +2332,16 @@
         <v>0.44756944444444446</v>
       </c>
       <c r="H43" s="2">
-        <v>0.23923611111111112</v>
+        <v>0.57256944444444446</v>
       </c>
       <c r="I43" s="2">
-        <v>0.23923611111111112</v>
+        <v>0.69756944444444446</v>
       </c>
       <c r="J43" s="2">
-        <v>0.23923611111111112</v>
+        <v>0.82256944444444446</v>
       </c>
       <c r="K43" s="2">
-        <v>0.23923611111111112</v>
+        <v>0.94756944444444446</v>
       </c>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.3">
@@ -2455,16 +2428,16 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="H46" s="2">
-        <v>0.23958333333333334</v>
+        <v>0.57291666666666663</v>
       </c>
       <c r="I46" s="2">
-        <v>0.23958333333333334</v>
+        <v>0.69791666666666663</v>
       </c>
       <c r="J46" s="2">
-        <v>0.23958333333333334</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="K46" s="2">
-        <v>0.23958333333333334</v>
+        <v>0.94791666666666663</v>
       </c>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.3">
@@ -2545,16 +2518,16 @@
         <v>0.44826388888888885</v>
       </c>
       <c r="H49" s="2">
-        <v>0.23993055555555554</v>
+        <v>0.57326388888888891</v>
       </c>
       <c r="I49" s="2">
-        <v>0.23993055555555554</v>
+        <v>0.69826388888888891</v>
       </c>
       <c r="J49" s="2">
-        <v>0.23993055555555554</v>
+        <v>0.82326388888888891</v>
       </c>
       <c r="K49" s="2">
-        <v>0.23993055555555554</v>
+        <v>0.94826388888888891</v>
       </c>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.3">
@@ -2635,16 +2608,16 @@
         <v>0.44861111111111113</v>
       </c>
       <c r="H52" s="2">
-        <v>0.24027777777777778</v>
+        <v>0.57361111111111118</v>
       </c>
       <c r="I52" s="2">
-        <v>0.24027777777777778</v>
+        <v>0.69861111111111107</v>
       </c>
       <c r="J52" s="2">
-        <v>0.24027777777777778</v>
+        <v>0.69861111111111107</v>
       </c>
       <c r="K52" s="2">
-        <v>0.24027777777777778</v>
+        <v>0.94861111111111107</v>
       </c>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.3">
@@ -2754,16 +2727,16 @@
         <v>0.44930555555555557</v>
       </c>
       <c r="H56" s="2">
-        <v>0.24097222222222223</v>
+        <v>0.57430555555555551</v>
       </c>
       <c r="I56" s="2">
-        <v>0.24097222222222223</v>
+        <v>0.69930555555555562</v>
       </c>
       <c r="J56" s="2">
-        <v>0.24097222222222223</v>
+        <v>0.82430555555555562</v>
       </c>
       <c r="K56" s="2">
-        <v>0.24097222222222223</v>
+        <v>0.94930555555555562</v>
       </c>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.3">
@@ -2873,16 +2846,16 @@
         <v>0.45</v>
       </c>
       <c r="H60" s="2">
-        <v>0.24166666666666667</v>
+        <v>0.57500000000000007</v>
       </c>
       <c r="I60" s="2">
-        <v>0.24166666666666667</v>
+        <v>0.70000000000000007</v>
       </c>
       <c r="J60" s="2">
-        <v>0.24166666666666667</v>
+        <v>0.82500000000000007</v>
       </c>
       <c r="K60" s="2">
-        <v>0.24166666666666667</v>
+        <v>0.95000000000000007</v>
       </c>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.3">
@@ -2992,16 +2965,16 @@
         <v>0.45034722222222223</v>
       </c>
       <c r="H64" s="2">
-        <v>0.24201388888888889</v>
+        <v>0.57534722222222223</v>
       </c>
       <c r="I64" s="2">
-        <v>0.24201388888888889</v>
+        <v>0.70034722222222223</v>
       </c>
       <c r="J64" s="2">
-        <v>0.24201388888888889</v>
+        <v>0.82534722222222223</v>
       </c>
       <c r="K64" s="2">
-        <v>0.24201388888888889</v>
+        <v>0.95034722222222223</v>
       </c>
     </row>
     <row r="65" spans="2:11" x14ac:dyDescent="0.3">
@@ -3053,16 +3026,16 @@
         <v>0.45057870370370368</v>
       </c>
       <c r="H66" s="2">
-        <v>0.24224537037037039</v>
+        <v>0.57557870370370368</v>
       </c>
       <c r="I66" s="2">
-        <v>0.24224537037037039</v>
+        <v>0.70057870370370379</v>
       </c>
       <c r="J66" s="2">
-        <v>0.24224537037037039</v>
+        <v>0.82557870370370379</v>
       </c>
       <c r="K66" s="2">
-        <v>0.24224537037037039</v>
+        <v>0.95057870370370379</v>
       </c>
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.3">
@@ -3143,16 +3116,16 @@
         <v>0.45069444444444445</v>
       </c>
       <c r="H69" s="2">
-        <v>0.24236111111111111</v>
+        <v>0.5756944444444444</v>
       </c>
       <c r="I69" s="2">
-        <v>0.24236111111111111</v>
+        <v>0.7006944444444444</v>
       </c>
       <c r="J69" s="2">
-        <v>0.24236111111111111</v>
+        <v>0.8256944444444444</v>
       </c>
       <c r="K69" s="2">
-        <v>0.24236111111111111</v>
+        <v>0.9506944444444444</v>
       </c>
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.3">
@@ -3291,16 +3264,16 @@
         <v>0.45104166666666662</v>
       </c>
       <c r="H74" s="2">
-        <v>0.24270833333333333</v>
+        <v>0.57604166666666667</v>
       </c>
       <c r="I74" s="2">
-        <v>0.24270833333333333</v>
+        <v>0.70104166666666667</v>
       </c>
       <c r="J74" s="2">
-        <v>0.24270833333333333</v>
+        <v>0.82604166666666667</v>
       </c>
       <c r="K74" s="2">
-        <v>0.24270833333333333</v>
+        <v>0.95104166666666667</v>
       </c>
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.3">
@@ -3439,16 +3412,16 @@
         <v>0.45173611111111112</v>
       </c>
       <c r="H79" s="2">
-        <v>0.24340277777777777</v>
+        <v>0.57673611111111112</v>
       </c>
       <c r="I79" s="2">
-        <v>0.24340277777777777</v>
+        <v>0.70173611111111101</v>
       </c>
       <c r="J79" s="2">
-        <v>0.24340277777777777</v>
+        <v>0.82673611111111101</v>
       </c>
       <c r="K79" s="2">
-        <v>0.24340277777777777</v>
+        <v>0.95173611111111101</v>
       </c>
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.3">
@@ -3558,16 +3531,16 @@
         <v>0.45208333333333334</v>
       </c>
       <c r="H83" s="4">
-        <v>0.24374999999999999</v>
+        <v>0.57708333333333328</v>
       </c>
       <c r="I83" s="4">
-        <v>0.24374999999999999</v>
+        <v>0.70208333333333339</v>
       </c>
       <c r="J83" s="4">
-        <v>0.24374999999999999</v>
+        <v>0.82708333333333339</v>
       </c>
       <c r="K83" s="4">
-        <v>0.24374999999999999</v>
+        <v>0.95208333333333339</v>
       </c>
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.3">
@@ -3677,16 +3650,16 @@
         <v>0.45266203703703706</v>
       </c>
       <c r="H87" s="4">
-        <v>0.24432870370370371</v>
+        <v>0.577662037037037</v>
       </c>
       <c r="I87" s="4">
-        <v>0.24432870370370371</v>
+        <v>0.702662037037037</v>
       </c>
       <c r="J87" s="4">
-        <v>0.24432870370370371</v>
+        <v>0.827662037037037</v>
       </c>
       <c r="K87" s="4">
-        <v>0.24432870370370371</v>
+        <v>0.952662037037037</v>
       </c>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.3">
@@ -4173,16 +4146,16 @@
         <v>0.45416666666666666</v>
       </c>
       <c r="H104" s="2">
-        <v>0.24583333333333335</v>
+        <v>0.57916666666666672</v>
       </c>
       <c r="I104" s="2">
-        <v>0.24583333333333335</v>
+        <v>0.70416666666666661</v>
       </c>
       <c r="J104" s="2">
-        <v>0.24583333333333335</v>
+        <v>0.82916666666666661</v>
       </c>
       <c r="K104" s="2">
-        <v>0.24583333333333335</v>
+        <v>0.95416666666666661</v>
       </c>
     </row>
     <row r="105" spans="2:11" x14ac:dyDescent="0.3">
@@ -4234,16 +4207,16 @@
         <v>0.4548611111111111</v>
       </c>
       <c r="H106" s="2">
-        <v>0.24652777777777779</v>
+        <v>0.57986111111111105</v>
       </c>
       <c r="I106" s="2">
-        <v>0.24652777777777779</v>
+        <v>0.70486111111111116</v>
       </c>
       <c r="J106" s="2">
-        <v>0.24652777777777779</v>
+        <v>0.82986111111111116</v>
       </c>
       <c r="K106" s="2">
-        <v>0.24652777777777779</v>
+        <v>0.95486111111111116</v>
       </c>
     </row>
     <row r="107" spans="2:11" x14ac:dyDescent="0.3">
@@ -4295,16 +4268,16 @@
         <v>0.45520833333333338</v>
       </c>
       <c r="H108" s="4">
-        <v>0.24687499999999998</v>
+        <v>0.58020833333333333</v>
       </c>
       <c r="I108" s="4">
-        <v>0.24687499999999998</v>
+        <v>0.70520833333333333</v>
       </c>
       <c r="J108" s="4">
-        <v>0.24687499999999998</v>
+        <v>0.83020833333333333</v>
       </c>
       <c r="K108" s="4">
-        <v>0.24687499999999998</v>
+        <v>0.95520833333333333</v>
       </c>
     </row>
     <row r="109" spans="2:11" x14ac:dyDescent="0.3">
@@ -4443,16 +4416,16 @@
         <v>0.45624999999999999</v>
       </c>
       <c r="H113" s="2">
-        <v>0.24791666666666667</v>
+        <v>0.58124999999999993</v>
       </c>
       <c r="I113" s="2">
-        <v>0.24791666666666667</v>
+        <v>0.70624999999999993</v>
       </c>
       <c r="J113" s="2">
-        <v>0.24791666666666667</v>
+        <v>0.83124999999999993</v>
       </c>
       <c r="K113" s="2">
-        <v>0.24791666666666667</v>
+        <v>0.95624999999999993</v>
       </c>
     </row>
     <row r="114" spans="2:11" x14ac:dyDescent="0.3">
@@ -4562,16 +4535,16 @@
         <v>0.45694444444444443</v>
       </c>
       <c r="H117" s="2">
-        <v>0.24861111111111112</v>
+        <v>0.58194444444444449</v>
       </c>
       <c r="I117" s="2">
-        <v>0.24861111111111112</v>
+        <v>0.70694444444444438</v>
       </c>
       <c r="J117" s="2">
-        <v>0.24861111111111112</v>
+        <v>0.83194444444444438</v>
       </c>
       <c r="K117" s="2">
-        <v>0.24861111111111112</v>
+        <v>0.95694444444444438</v>
       </c>
     </row>
     <row r="118" spans="2:11" x14ac:dyDescent="0.3">
@@ -4623,16 +4596,16 @@
         <v>0.45763888888888887</v>
       </c>
       <c r="H119" s="2">
-        <v>0.24930555555555556</v>
+        <v>0.58263888888888882</v>
       </c>
       <c r="I119" s="2">
-        <v>0.24930555555555556</v>
+        <v>0.70763888888888893</v>
       </c>
       <c r="J119" s="2">
-        <v>0.24930555555555556</v>
+        <v>0.83263888888888893</v>
       </c>
       <c r="K119" s="2">
-        <v>0.24930555555555556</v>
+        <v>0.95763888888888893</v>
       </c>
     </row>
     <row r="120" spans="2:11" x14ac:dyDescent="0.3">
@@ -4742,16 +4715,16 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="H123" s="4">
-        <v>0.25</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="I123" s="4">
-        <v>0.25</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="J123" s="4">
-        <v>0.25</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="K123" s="4">
-        <v>0.25</v>
+        <v>0.95833333333333337</v>
       </c>
     </row>
     <row r="124" spans="2:11" x14ac:dyDescent="0.3">

--- a/Routes.xlsx
+++ b/Routes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eugk\Documents\iot\project\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99469319-808E-4651-9AE7-A8DBE8DE98E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8470168-63BA-400C-BA0B-641C9511A80F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E451EE4A-2127-43C9-9A50-5536E739BF9B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="190">
   <si>
     <t>Intracom</t>
   </si>
@@ -563,9 +563,6 @@
     <t>Haradros River</t>
   </si>
   <si>
-    <t>Polytechnic</t>
-  </si>
-  <si>
     <t>Conference Center</t>
   </si>
   <si>
@@ -594,6 +591,21 @@
   </si>
   <si>
     <t>University of Patras Chancellors Office</t>
+  </si>
+  <si>
+    <t>38.27920089206051, 21.76724285398675</t>
+  </si>
+  <si>
+    <t>38.281657955154586, 21.770596375604853</t>
+  </si>
+  <si>
+    <t>38.284356703219245, 21.77277117748854</t>
+  </si>
+  <si>
+    <t>38.28977270490379, 21.78496964937884</t>
+  </si>
+  <si>
+    <t>Polytechnio</t>
   </si>
 </sst>
 </file>
@@ -991,13 +1003,13 @@
   <sheetData>
     <row r="1" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.3">
@@ -2317,7 +2329,7 @@
         <v>139</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>42</v>
@@ -3098,7 +3110,7 @@
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
-        <v>77</v>
+        <v>185</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>161</v>
@@ -3394,7 +3406,7 @@
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B79" s="1" t="s">
-        <v>77</v>
+        <v>186</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>163</v>
@@ -3513,7 +3525,7 @@
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B83" s="1" t="s">
-        <v>77</v>
+        <v>187</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>164</v>
@@ -4131,7 +4143,7 @@
         <v>114</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D104" t="s">
         <v>70</v>
@@ -4192,7 +4204,7 @@
         <v>116</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="D106" t="s">
         <v>71</v>
@@ -4250,10 +4262,10 @@
     </row>
     <row r="108" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B108" t="s">
-        <v>77</v>
+        <v>188</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D108" t="s">
         <v>72</v>
@@ -4401,7 +4413,7 @@
         <v>122</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D113" t="s">
         <v>73</v>
@@ -4520,7 +4532,7 @@
         <v>126</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D117" t="s">
         <v>74</v>
@@ -4581,7 +4593,7 @@
         <v>128</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D119" t="s">
         <v>75</v>
@@ -4700,7 +4712,7 @@
         <v>132</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D123" t="s">
         <v>76</v>
